--- a/Full_Timetable.xlsx
+++ b/Full_Timetable.xlsx
@@ -8,8 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="CS1A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CS3A" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CS3B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IT1A" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="IT1B" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IT1C" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="IT2A" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="IT2B" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="IT2C" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="IT3A" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="IT3B" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="IT3C" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="IT4A" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="IT4B" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="IT4C" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -473,11 +483,7 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>Understanding the Self (R100B)</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
     </row>
@@ -499,6 +505,593 @@
           <t>10-11</t>
         </is>
       </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Understanding the Self (R100B)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Understanding the Self (R100B)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics (R100B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Information and Project Management (R100C)</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Information and Project Management (R100A)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Platform Technologies (R100C)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Data Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Information and Project Management (R100C)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics (R100B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Data Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Data Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>Life and Works of Rizal (R100B)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Social Issues &amp; Ethics in Computing (R100B)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Multimedia Systems (R100B)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="1" t="inlineStr">
+        <is>
+          <t>Information Assurance &amp; Security 2 (R100C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Information Assurance &amp; Security 2 (R100C)</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Information Assurance &amp; Security 2 (R100C)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing (R100C)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing (R100C)</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing (R100C)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -547,6 +1140,187 @@
           <t>2-3</t>
         </is>
       </c>
+      <c r="B8" s="1" t="inlineStr">
+        <is>
+          <t>Social Issues &amp; Ethics in Computing (R100A)</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="inlineStr">
+        <is>
+          <t>Social Issues &amp; Ethics in Computing (R100B)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing (R100C)</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing (R100C)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>Social Issues &amp; Ethics in Computing (R100B)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Social Issues &amp; Ethics in Computing (R100B)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -559,11 +1333,7 @@
           <t>3-4</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Understanding the Self (R100B)</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -578,7 +1348,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Understanding the Self (R100C)</t>
+          <t>Capstone Project Writing (R100C)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -641,18 +1411,26 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>Linear Algebra (R100A)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>Operations Research (R100B)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -661,16 +1439,24 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Software Engineering (R100A)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Information Assurance (R100B)</t>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab1)</t>
         </is>
       </c>
     </row>
@@ -680,23 +1466,27 @@
           <t>10-11</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Automata Theory (R100A)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>Automata Theory (R100C)</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>Automata Theory (R100B)</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -704,23 +1494,11 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Distributed Systems (R100A)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Information Assurance (R100C)</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Software Engineering (R100C)</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -741,21 +1519,9 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Operations Research (R100A)</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Linear Algebra (R100B)</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Linear Algebra (R100A)</t>
-        </is>
-      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -766,21 +1532,21 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Distributed Systems Lab (Lab2)</t>
+          <t>Computer Networks 1 Lab (Lab1)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Lab (Lab2)</t>
+          <t>Computer Networks 1 Lab (Lab1)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Information Assurance Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>CWTS 1/ROTC 1 (R100C)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -790,25 +1556,21 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Distributed Systems Lab (Lab2)</t>
+          <t>Computer Networks 1 Lab (Lab1)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>Operations Research (R100B)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Information Assurance Lab (Lab2)</t>
-        </is>
-      </c>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Understanding the Self (R100C)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -818,25 +1580,21 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Distributed Systems Lab (Lab2)</t>
+          <t>Computer Networks 1 Lab (Lab1)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>Distributed Systems (R100B)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Information Assurance Lab (Lab2)</t>
-        </is>
-      </c>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Movement Competency Training (MCT) (R100B)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -894,16 +1652,24 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Information Assurance Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Linear Algebra (R100A)</t>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
         </is>
       </c>
     </row>
@@ -913,27 +1679,27 @@
           <t>9-10</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Distributed Systems (R100C)</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Operations Research (R100C)</t>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Information Assurance Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Operations Research (R100C)</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -942,18 +1708,26 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Operations Research (R100C)</t>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Information Assurance Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -961,21 +1735,9 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Information Assurance (R100C)</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Information Assurance (R100C)</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Distributed Systems (R100B)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
     </row>
@@ -997,31 +1759,11 @@
           <t>1-2</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>Automata Theory (R100B)</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>Linear Algebra (R100C)</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Automata Theory (R100C)</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>Software Engineering (R100C)</t>
-        </is>
-      </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Automata Theory (R100A)</t>
-        </is>
-      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1029,17 +1771,1475 @@
           <t>2-3</t>
         </is>
       </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>CWTS 1/ROTC 1 (R100A)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Movement Competency Training (MCT) (R100C)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>CWTS 1/ROTC 1 (R100B)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Movement Competency Training (MCT) (R100A)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Movement Competency Training (MCT) (R100B)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>CWTS 1/ROTC 1 (R100B)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Reading Visual Art (R100B)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Database Systems Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>Database Systems (R100A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Database Systems Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Ethics (R100B)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Database Systems Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Dance (R100B)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Database Systems (R100A)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Operating System (R100B)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Fundamentals of Accounting for IT (R100B)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Ethics (R100B)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Dance (R100C)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Environmental Science (R100B)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development (R100B)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Environmental Science (R100B)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Fundamentals of Accounting for IT (R100B)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Database Systems Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Data Structures &amp; Algorithms (R100A)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Database Systems Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" s="1" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development (R100C)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Data Structures Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Database Systems Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>Dance (R100B)</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Data Analytics (R100C)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Data Analytics Lab (Lab1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Data Analytics Lab (Lab1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>Information and Project Management (R100B)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Data Analytics Lab (Lab1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Platform Technologies (R100C)</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>Life and Works of Rizal (R100C)</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>Platform Technologies (R100B)</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Platform Technologies (R100B)</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>Platform Technologies (R100B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Life and Works of Rizal (R100B)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Life and Works of Rizal (R100B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E8" s="1" t="inlineStr">
+        <is>
+          <t>Information and Project Management (R100C)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" s="1" t="inlineStr">
+        <is>
+          <t>Life and Works of Rizal (R100B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>4-5</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Mon</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Tue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Wed</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Thu</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Fri</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>8-9</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>9-10</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10-11</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>11-12</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Life and Works of Rizal (R100C)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics (R100B)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Lab (Lab1)</t>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Distributed Systems Lab (Lab1)</t>
+          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
         </is>
       </c>
     </row>
@@ -1050,20 +3250,20 @@
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Software Engineering (R100B)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Lab (Lab1)</t>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Distributed Systems Lab (Lab1)</t>
+          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
         </is>
       </c>
     </row>
@@ -1073,21 +3273,21 @@
           <t>4-5</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>Linear Algebra (R100B)</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Software Engineering Lab (Lab1)</t>
+          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Distributed Systems Lab (Lab1)</t>
+          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
         </is>
       </c>
     </row>

--- a/Full_Timetable.xlsx
+++ b/Full_Timetable.xlsx
@@ -494,9 +494,17 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Understanding the Self (R100A)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Understanding the Self (R100C)</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -505,11 +513,7 @@
           <t>10-11</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Understanding the Self (R100B)</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
@@ -521,11 +525,7 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Understanding the Self (R100B)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -647,17 +647,13 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Information and Project Management Lab (Lab2)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Information and Project Management Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -667,22 +663,14 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>Information and Project Management Lab (Lab2)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Information and Project Management Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Fundamentals of Business Analytics (R100B)</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -690,26 +678,14 @@
           <t>10-11</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Information and Project Management (R100C)</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>Information and Project Management (R100A)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Information and Project Management Lab (Lab2)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Information and Project Management Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -718,11 +694,7 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Platform Technologies (R100C)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -760,25 +732,13 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Information and Project Management Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Data Analytics Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>Information and Project Management (R100C)</t>
-        </is>
-      </c>
+          <t>Data Analytics Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>Fundamentals of Business Analytics (R100B)</t>
-        </is>
-      </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -788,14 +748,10 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Information and Project Management Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Data Analytics Lab (Lab2)</t>
-        </is>
-      </c>
+          <t>Data Analytics Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
@@ -808,21 +764,13 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Information and Project Management Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Data Analytics Lab (Lab2)</t>
-        </is>
-      </c>
+          <t>Data Analytics Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>Life and Works of Rizal (R100B)</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -881,9 +829,17 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Information Assurance &amp; Security 2 Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Multimedia Systems Lab (Lab2)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -893,9 +849,17 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Information Assurance &amp; Security 2 Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Multimedia Systems Lab (Lab2)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -903,15 +867,19 @@
           <t>10-11</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Social Issues &amp; Ethics in Computing (R100B)</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Information Assurance &amp; Security 2 Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Multimedia Systems Lab (Lab2)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -919,11 +887,7 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Multimedia Systems (R100B)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -939,11 +903,7 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>Information Assurance &amp; Security 2 (R100C)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -963,16 +923,12 @@
           <t>2-3</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Information Assurance &amp; Security 2 (R100C)</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Information Assurance &amp; Security 2 (R100C)</t>
-        </is>
-      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -983,7 +939,11 @@
           <t>3-4</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
@@ -995,7 +955,11 @@
           <t>4-5</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
@@ -1057,7 +1021,11 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Multimedia Systems (R100C)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
@@ -1069,21 +1037,9 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>Capstone Project Writing (R100C)</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Capstone Project Writing (R100C)</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Capstone Project Writing (R100C)</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1104,7 +1060,11 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>Multimedia Systems (R100C)</t>
+        </is>
+      </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -1128,10 +1088,22 @@
           <t>1-2</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Multimedia Systems (R100C)</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Information Assurance &amp; Security 2 (R100A)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" s="1" t="inlineStr">
+        <is>
+          <t>Information Assurance &amp; Security 2 (R100A)</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
@@ -1140,19 +1112,19 @@
           <t>2-3</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>Social Issues &amp; Ethics in Computing (R100A)</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>Social Issues &amp; Ethics in Computing (R100B)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" s="1" t="inlineStr">
+        <is>
+          <t>Multimedia Systems (R100C)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1160,17 +1132,13 @@
           <t>3-4</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>Capstone Project Writing (R100C)</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>Capstone Project Writing (R100C)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
     </row>
@@ -1181,12 +1149,12 @@
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>Social Issues &amp; Ethics in Computing (R100B)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Capstone Project Writing Lab (Lab2)</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
@@ -1259,11 +1227,7 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Social Issues &amp; Ethics in Computing (R100B)</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
     </row>
@@ -1313,7 +1277,11 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Social Issues &amp; Ethics in Computing (R100B)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1346,11 +1314,7 @@
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>Capstone Project Writing (R100C)</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -1411,26 +1375,10 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1439,26 +1387,10 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1467,26 +1399,10 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1530,22 +1446,14 @@
           <t>2-3</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>CWTS 1/ROTC 1 (R100C)</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>Computer Programming 1 (R100C)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1554,22 +1462,14 @@
           <t>3-4</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Understanding the Self (R100C)</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>Understanding the Self (R100A)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -1578,22 +1478,14 @@
           <t>4-5</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>Movement Competency Training (MCT) (R100B)</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>Science, Technology, and Society (R100A)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
@@ -1652,26 +1544,10 @@
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1680,26 +1556,14 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Movement Competency Training (MCT) (R100A)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1708,26 +1572,10 @@
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1771,27 +1619,19 @@
           <t>2-3</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>CWTS 1/ROTC 1 (R100A)</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1799,27 +1639,19 @@
           <t>3-4</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Movement Competency Training (MCT) (R100C)</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1827,27 +1659,19 @@
           <t>4-5</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>CWTS 1/ROTC 1 (R100B)</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Computer Networks 1 Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Platform Technologies Lab (Lab1)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1907,11 +1731,7 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -1920,18 +1740,10 @@
           <t>9-10</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Movement Competency Training (MCT) (R100A)</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -1940,18 +1752,10 @@
           <t>10-11</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Movement Competency Training (MCT) (R100B)</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -1960,11 +1764,7 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>CWTS 1/ROTC 1 (R100B)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -2000,21 +1800,9 @@
           <t>2-3</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
     </row>
@@ -2024,21 +1812,9 @@
           <t>3-4</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
     </row>
@@ -2048,26 +1824,10 @@
           <t>4-5</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Computer Networks 1 Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Platform Technologies Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>Reading Visual Art (R100B)</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
@@ -2127,17 +1887,9 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Database Systems Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>Database Systems (R100A)</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2146,13 +1898,17 @@
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Database Systems Lab (Lab1)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="C3" s="1" t="inlineStr">
+        <is>
+          <t>Introduction to Game Development (R100C)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Data Structures &amp; Algorithms (R100C)</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -2161,17 +1917,9 @@
           <t>10-11</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Ethics (R100B)</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Database Systems Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
     </row>
@@ -2181,11 +1929,7 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Dance (R100B)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -2221,11 +1965,7 @@
           <t>2-3</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Operating System Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>Data Structures Lab (Lab2)</t>
@@ -2241,22 +1981,14 @@
           <t>3-4</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Operating System Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Data Structures Lab (Lab2)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Database Systems (R100A)</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2265,22 +1997,14 @@
           <t>4-5</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Operating System Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Data Structures Lab (Lab2)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>Operating System (R100B)</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
@@ -2340,21 +2064,9 @@
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Data Structures Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Operating System Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2364,21 +2076,9 @@
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Data Structures Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Operating System Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2386,27 +2086,11 @@
           <t>10-11</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Fundamentals of Accounting for IT (R100B)</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Data Structures Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Operating System Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2416,7 +2100,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>Ethics (R100B)</t>
+          <t>Ethics (R100C)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
@@ -2430,7 +2114,11 @@
           <t>12-1</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="1" t="inlineStr">
+        <is>
+          <t>Environmental Science (R100B)</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
@@ -2442,7 +2130,11 @@
           <t>1-2</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" s="1" t="inlineStr">
+        <is>
+          <t>Dance (R100B)</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
@@ -2454,20 +2146,12 @@
           <t>2-3</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>Dance (R100C)</t>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab1)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
@@ -2478,20 +2162,12 @@
           <t>3-4</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Environmental Science (R100B)</t>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab1)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -2502,20 +2178,12 @@
           <t>4-5</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development (R100B)</t>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Operating System Lab (Lab1)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
@@ -2578,20 +2246,12 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Operating System Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab1)</t>
-        </is>
-      </c>
+          <t>Data Structures Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Data Structures Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2602,20 +2262,12 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Operating System Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab1)</t>
-        </is>
-      </c>
+          <t>Data Structures Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Data Structures Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2623,27 +2275,15 @@
           <t>10-11</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Environmental Science (R100B)</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Operating System Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development Lab (Lab1)</t>
-        </is>
-      </c>
+          <t>Data Structures Lab (Lab1)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Data Structures Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2651,11 +2291,7 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Fundamentals of Accounting for IT (R100B)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
@@ -2670,7 +2306,11 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" s="1" t="inlineStr">
+        <is>
+          <t>Ethics (R100A)</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -2696,17 +2336,9 @@
           <t>Data Structures Lab (Lab2)</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Database Systems Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>Data Structures &amp; Algorithms (R100A)</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2720,17 +2352,9 @@
           <t>Data Structures Lab (Lab2)</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Database Systems Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>Introduction to Game Development (R100C)</t>
-        </is>
-      </c>
+      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -2744,17 +2368,9 @@
           <t>Data Structures Lab (Lab2)</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Database Systems Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>Dance (R100B)</t>
-        </is>
-      </c>
+      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
@@ -2812,31 +2428,23 @@
           <t>8-9</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>Data Analytics (R100C)</t>
-        </is>
-      </c>
+      <c r="B2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Information and Project Management Lab (Lab1)</t>
+          <t>Computer Networks 1 Lab (Lab2)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+          <t>Data Analytics Lab (Lab2)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Data Analytics Lab (Lab1)</t>
-        </is>
-      </c>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2847,24 +2455,20 @@
       <c r="B3" t="inlineStr"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Information and Project Management Lab (Lab1)</t>
+          <t>Computer Networks 1 Lab (Lab2)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+          <t>Data Analytics Lab (Lab2)</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Data Analytics Lab (Lab1)</t>
-        </is>
-      </c>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2872,31 +2476,23 @@
           <t>10-11</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>Information and Project Management (R100B)</t>
-        </is>
-      </c>
+      <c r="B4" t="inlineStr"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Information and Project Management Lab (Lab1)</t>
+          <t>Computer Networks 1 Lab (Lab2)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
+          <t>Data Analytics Lab (Lab2)</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Data Analytics Lab (Lab1)</t>
-        </is>
-      </c>
+          <t>Information and Project Management Lab (Lab2)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2904,31 +2500,11 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Platform Technologies (R100C)</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>Life and Works of Rizal (R100C)</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>Platform Technologies (R100B)</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>Platform Technologies (R100B)</t>
-        </is>
-      </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>Platform Technologies (R100B)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2950,17 +2526,9 @@
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>Life and Works of Rizal (R100B)</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>Life and Works of Rizal (R100B)</t>
-        </is>
-      </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2970,24 +2538,12 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Information and Project Management Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
           <t>Computer Networks 1 Lab (Lab1)</t>
         </is>
       </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>Information and Project Management (R100C)</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
@@ -2998,25 +2554,13 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Information and Project Management Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
           <t>Computer Networks 1 Lab (Lab1)</t>
         </is>
       </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>Life and Works of Rizal (R100B)</t>
-        </is>
-      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3026,19 +2570,11 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Information and Project Management Lab (Lab2)</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
           <t>Computer Networks 1 Lab (Lab1)</t>
         </is>
       </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
     </row>
@@ -3099,18 +2635,18 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+          <t>Platform Technologies Lab (Lab1)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+          <t>Platform Technologies Lab (Lab2)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+          <t>System Administration &amp; Maintenance Lab (Lab1)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
@@ -3123,18 +2659,18 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+          <t>Platform Technologies Lab (Lab1)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+          <t>Platform Technologies Lab (Lab2)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+          <t>System Administration &amp; Maintenance Lab (Lab1)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
@@ -3147,18 +2683,18 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+          <t>Platform Technologies Lab (Lab1)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+          <t>Platform Technologies Lab (Lab2)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab2)</t>
+          <t>System Administration &amp; Maintenance Lab (Lab1)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
@@ -3169,19 +2705,11 @@
           <t>11-12</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>Life and Works of Rizal (R100C)</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3189,19 +2717,15 @@
           <t>12-1</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>Fundamentals of Business Analytics (R100B)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" s="1" t="inlineStr">
+        <is>
+          <t>Life and Works of Rizal (R100A)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
-        </is>
-      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3210,12 +2734,20 @@
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+      <c r="C7" s="1" t="inlineStr">
+        <is>
+          <t>Platform Technologies (R100A)</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>Platform Technologies (R100B)</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
+      <c r="F7" s="1" t="inlineStr">
+        <is>
+          <t>Fundamentals of Business Analytics (R100B)</t>
         </is>
       </c>
     </row>
@@ -3227,11 +2759,7 @@
       </c>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Fundamentals of Business Analytics Lab (Lab2)</t>
@@ -3239,7 +2767,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
+          <t>System Administration &amp; Maintenance Lab (Lab1)</t>
         </is>
       </c>
     </row>
@@ -3251,11 +2779,7 @@
       </c>
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Fundamentals of Business Analytics Lab (Lab2)</t>
@@ -3263,7 +2787,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
+          <t>System Administration &amp; Maintenance Lab (Lab1)</t>
         </is>
       </c>
     </row>
@@ -3275,11 +2799,7 @@
       </c>
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>System Administration &amp; Maintenance Lab (Lab2)</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Fundamentals of Business Analytics Lab (Lab2)</t>
@@ -3287,7 +2807,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Fundamentals of Business Analytics Lab (Lab1)</t>
+          <t>System Administration &amp; Maintenance Lab (Lab1)</t>
         </is>
       </c>
     </row>
